--- a/02_GD32F407_FreeRTOS_Timer/Project/GD32F407_analysis.xlsx
+++ b/02_GD32F407_FreeRTOS_Timer/Project/GD32F407_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="43">
   <si>
     <t>GD32F407</t>
   </si>
@@ -57,9 +57,6 @@
   </si>
   <si>
     <t>gd32f4xx_usart.o</t>
-  </si>
-  <si>
-    <t>gd32f4xx_timer.o</t>
   </si>
   <si>
     <t>printf3.o</t>
@@ -236,9 +233,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$36</c:f>
+              <c:f>ram_percent!$A$3:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="34"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
@@ -275,7 +272,7 @@
                 <c:pt idx="11">
                   <c:v>bsp_keys.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="32">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -283,47 +280,47 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$36</c:f>
+              <c:f>ram_percent!$B$3:$B$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
-                  <c:v>96.22624969482422</c:v>
+                  <c:v>96.21660614013672</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.287559032440186</c:v>
+                  <c:v>1.287430047988892</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.282549023628235</c:v>
+                  <c:v>1.282420516014099</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.001991510391235</c:v>
+                  <c:v>1.001891016960144</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.08015931397676468</c:v>
+                  <c:v>0.0801512822508812</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.07514935731887817</c:v>
+                  <c:v>0.07514183223247528</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.01502987183630467</c:v>
+                  <c:v>0.02504727616906166</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.01127240434288979</c:v>
+                  <c:v>0.01127127464860678</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.005009957123547792</c:v>
+                  <c:v>0.005009455140680075</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.005009957123547792</c:v>
+                  <c:v>0.005009455140680075</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.005009957123547792</c:v>
+                  <c:v>0.005009455140680075</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.005009957123547792</c:v>
-                </c:pt>
-                <c:pt idx="33">
+                  <c:v>0.005009455140680075</c:v>
+                </c:pt>
+                <c:pt idx="32">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -391,17 +388,17 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$36</c:f>
+              <c:f>flash_percent!$A$3:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="34"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>tasks.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>timers.o</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>queue.o</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>timers.o</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>port.o</c:v>
@@ -419,81 +416,78 @@
                   <c:v>usart0.o</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>gd32f4xx_timer.o</c:v>
+                  <c:v>system_gd32f4xx.o</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>main.o</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>system_gd32f4xx.o</c:v>
+                  <c:v>printf3.o</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>printf3.o</c:v>
+                  <c:v>exti.o</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>exti.o</c:v>
+                  <c:v>gd32f4xx_dma.o</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>gd32f4xx_dma.o</c:v>
+                  <c:v>startup_gd32f407_427.o</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>startup_gd32f407_427.o</c:v>
+                  <c:v>gd32f4xx_rcu.o</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>gd32f4xx_rcu.o</c:v>
+                  <c:v>gd32f4xx_gpio.o</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>gd32f4xx_gpio.o</c:v>
+                  <c:v>bsp_keys.o</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>bsp_keys.o</c:v>
+                  <c:v>gd32f4xx_misc.o</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>gd32f4xx_misc.o</c:v>
+                  <c:v>list.o</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>list.o</c:v>
+                  <c:v>systick.o</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>systick.o</c:v>
+                  <c:v>init.o</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>init.o</c:v>
+                  <c:v>uidiv.o</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>uidiv.o</c:v>
+                  <c:v>puts.o</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>puts.o</c:v>
+                  <c:v>memseta.o</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>memseta.o</c:v>
+                  <c:v>memcpya.o</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>memcpya.o</c:v>
+                  <c:v>handlers.o</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>handlers.o</c:v>
+                  <c:v>gd32f4xx_exti.o</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>gd32f4xx_exti.o</c:v>
+                  <c:v>gd32f4xx_it.o</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>gd32f4xx_it.o</c:v>
+                  <c:v>entry9a.o</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>entry9a.o</c:v>
+                  <c:v>entry2.o</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>entry2.o</c:v>
+                  <c:v>stdout.o</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>stdout.o</c:v>
+                  <c:v>entry5.o</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>entry5.o</c:v>
-                </c:pt>
-                <c:pt idx="33">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -501,110 +495,107 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$36</c:f>
+              <c:f>flash_percent!$B$3:$B$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="34"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
-                  <c:v>23.20836639404297</c:v>
+                  <c:v>24.21052551269531</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.527436256408691</c:v>
+                  <c:v>8.029196739196777</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.916108131408691</c:v>
+                  <c:v>7.85247802734375</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.754069328308106</c:v>
+                  <c:v>7.045716285705566</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.347278594970703</c:v>
+                  <c:v>5.578178882598877</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.890624046325684</c:v>
+                  <c:v>5.101805686950684</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.360315322875977</c:v>
+                  <c:v>4.548597812652588</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.154084205627441</c:v>
+                  <c:v>4.333461284637451</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.109891891479492</c:v>
+                  <c:v>4.102958202362061</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4.065699577331543</c:v>
+                  <c:v>3.657318592071533</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.933122158050537</c:v>
+                  <c:v>3.626584768295288</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.476467609405518</c:v>
+                  <c:v>3.611217737197876</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.461736679077148</c:v>
+                  <c:v>3.334613800048828</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.196582555770874</c:v>
+                  <c:v>3.28851318359375</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3.152390003204346</c:v>
+                  <c:v>2.212831258773804</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2.371657848358154</c:v>
+                  <c:v>2.105263233184815</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2.018118858337402</c:v>
+                  <c:v>1.813292384147644</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.738233804702759</c:v>
+                  <c:v>1.38301956653595</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.325771570205689</c:v>
+                  <c:v>1.15251636505127</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.104809641838074</c:v>
+                  <c:v>0.7376104593276978</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.7070781588554382</c:v>
+                  <c:v>0.3688052296638489</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.3535390794277191</c:v>
+                  <c:v>0.3380714654922485</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.3240774869918823</c:v>
+                  <c:v>0.2766039073467255</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.2651543021202087</c:v>
+                  <c:v>0.2766039073467255</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.2651543021202087</c:v>
+                  <c:v>0.2766039073467255</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.2651543021202087</c:v>
+                  <c:v>0.230503261089325</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.2209619134664536</c:v>
+                  <c:v>0.230503261089325</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.2209619134664536</c:v>
+                  <c:v>0.09220130741596222</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.08838476985692978</c:v>
+                  <c:v>0.06146753579378128</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.05892317742109299</c:v>
+                  <c:v>0.06146753579378128</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.05892317742109299</c:v>
+                  <c:v>0.03073376789689064</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.02946158871054649</c:v>
+                  <c:v>0.03073376789689064</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.02946158871054649</c:v>
-                </c:pt>
-                <c:pt idx="33">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -709,8 +700,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H36" totalsRowCount="1">
-  <autoFilter ref="A2:H35"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H35" totalsRowCount="1">
+  <autoFilter ref="A2:H34"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -726,8 +717,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H36" totalsRowCount="1">
-  <autoFilter ref="A2:H35"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H35" totalsRowCount="1">
+  <autoFilter ref="A2:H34"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -1027,7 +1018,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1040,28 +1031,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
         <v>36</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>37</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>38</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>39</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>40</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>41</v>
-      </c>
-      <c r="H2" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1069,7 +1060,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>96.22624969482422</v>
+        <v>96.21660614013672</v>
       </c>
       <c r="C3" s="1">
         <v>76828</v>
@@ -1095,7 +1086,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>1.287559032440186</v>
+        <v>1.287430047988892</v>
       </c>
       <c r="C4" s="1">
         <v>1028</v>
@@ -1121,7 +1112,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>1.282549023628235</v>
+        <v>1.282420516014099</v>
       </c>
       <c r="C5" s="1">
         <v>1024</v>
@@ -1147,7 +1138,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>1.001991510391235</v>
+        <v>1.001891016960144</v>
       </c>
       <c r="C6" s="1">
         <v>800</v>
@@ -1173,7 +1164,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.08015931397676468</v>
+        <v>0.0801512822508812</v>
       </c>
       <c r="C7" s="1">
         <v>64</v>
@@ -1199,16 +1190,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.07514935731887817</v>
+        <v>0.07514183223247528</v>
       </c>
       <c r="C8" s="1">
         <v>60</v>
       </c>
       <c r="D8" s="1">
-        <v>939</v>
+        <v>1045</v>
       </c>
       <c r="E8" s="1">
-        <v>918</v>
+        <v>1024</v>
       </c>
       <c r="F8" s="1">
         <v>21</v>
@@ -1225,16 +1216,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.01502987183630467</v>
+        <v>0.02504727616906166</v>
       </c>
       <c r="C9" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D9" s="1">
-        <v>552</v>
+        <v>476</v>
       </c>
       <c r="E9" s="1">
-        <v>552</v>
+        <v>476</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -1243,7 +1234,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1251,7 +1242,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.01127240434288979</v>
+        <v>0.01127127464860678</v>
       </c>
       <c r="C10" s="1">
         <v>9</v>
@@ -1277,7 +1268,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.005009957123547792</v>
+        <v>0.005009455140680075</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
@@ -1303,7 +1294,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.005009957123547792</v>
+        <v>0.005009455140680075</v>
       </c>
       <c r="C12" s="1">
         <v>4</v>
@@ -1329,7 +1320,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.005009957123547792</v>
+        <v>0.005009455140680075</v>
       </c>
       <c r="C13" s="1">
         <v>4</v>
@@ -1355,7 +1346,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.005009957123547792</v>
+        <v>0.005009455140680075</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
@@ -1376,35 +1367,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
-      <c r="A36" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36">
+    <row r="35" spans="1:8">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C36">
+      <c r="C35">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D36">
+      <c r="D35">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E36">
+      <c r="E35">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F36">
+      <c r="F35">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G36">
+      <c r="G35">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H36">
+      <c r="H35">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -1420,7 +1411,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1433,28 +1424,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" t="s">
         <v>38</v>
       </c>
-      <c r="D2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>39</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>40</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>41</v>
-      </c>
-      <c r="H2" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1462,7 +1453,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>23.20836639404297</v>
+        <v>24.21052551269531</v>
       </c>
       <c r="C3" s="1">
         <v>3151</v>
@@ -1485,54 +1476,54 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="2">
-        <v>7.527436256408691</v>
+        <v>8.029196739196777</v>
       </c>
       <c r="C4" s="1">
-        <v>1022</v>
+        <v>1045</v>
       </c>
       <c r="D4" s="1">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E4" s="1">
-        <v>1002</v>
+        <v>1024</v>
       </c>
       <c r="F4" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>6.916108131408691</v>
+        <v>7.85247802734375</v>
       </c>
       <c r="C5" s="1">
-        <v>939</v>
+        <v>1022</v>
       </c>
       <c r="D5" s="1">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E5" s="1">
-        <v>918</v>
+        <v>1002</v>
       </c>
       <c r="F5" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1540,7 +1531,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="2">
-        <v>6.754069328308106</v>
+        <v>7.045716285705566</v>
       </c>
       <c r="C6" s="1">
         <v>917</v>
@@ -1566,7 +1557,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="2">
-        <v>5.347278594970703</v>
+        <v>5.578178882598877</v>
       </c>
       <c r="C7" s="1">
         <v>726</v>
@@ -1592,7 +1583,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="2">
-        <v>4.890624046325684</v>
+        <v>5.101805686950684</v>
       </c>
       <c r="C8" s="1">
         <v>664</v>
@@ -1618,7 +1609,7 @@
         <v>13</v>
       </c>
       <c r="B9" s="2">
-        <v>4.360315322875977</v>
+        <v>4.548597812652588</v>
       </c>
       <c r="C9" s="1">
         <v>592</v>
@@ -1644,7 +1635,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="2">
-        <v>4.154084205627441</v>
+        <v>4.333461284637451</v>
       </c>
       <c r="C10" s="1">
         <v>564</v>
@@ -1667,25 +1658,25 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B11" s="2">
-        <v>4.109891891479492</v>
+        <v>4.102958202362061</v>
       </c>
       <c r="C11" s="1">
-        <v>558</v>
+        <v>534</v>
       </c>
       <c r="D11" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E11" s="1">
-        <v>558</v>
+        <v>530</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>
@@ -1696,16 +1687,16 @@
         <v>7</v>
       </c>
       <c r="B12" s="2">
-        <v>4.065699577331543</v>
+        <v>3.657318592071533</v>
       </c>
       <c r="C12" s="1">
-        <v>552</v>
+        <v>476</v>
       </c>
       <c r="D12" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E12" s="1">
-        <v>552</v>
+        <v>476</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -1714,30 +1705,30 @@
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B13" s="2">
-        <v>3.933122158050537</v>
+        <v>3.626584768295288</v>
       </c>
       <c r="C13" s="1">
-        <v>534</v>
+        <v>472</v>
       </c>
       <c r="D13" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>530</v>
+        <v>472</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H13" s="1">
         <v>0</v>
@@ -1748,16 +1739,16 @@
         <v>15</v>
       </c>
       <c r="B14" s="2">
-        <v>3.476467609405518</v>
+        <v>3.611217737197876</v>
       </c>
       <c r="C14" s="1">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -1774,16 +1765,16 @@
         <v>16</v>
       </c>
       <c r="B15" s="2">
-        <v>3.461736679077148</v>
+        <v>3.334613800048828</v>
       </c>
       <c r="C15" s="1">
-        <v>470</v>
+        <v>434</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>470</v>
+        <v>434</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -1797,54 +1788,54 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="B16" s="2">
-        <v>3.196582555770874</v>
+        <v>3.28851318359375</v>
       </c>
       <c r="C16" s="1">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="D16" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
       <c r="E16" s="1">
-        <v>434</v>
+        <v>36</v>
       </c>
       <c r="F16" s="1">
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B17" s="2">
-        <v>3.152390003204346</v>
+        <v>2.212831258773804</v>
       </c>
       <c r="C17" s="1">
-        <v>428</v>
+        <v>288</v>
       </c>
       <c r="D17" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>36</v>
+        <v>280</v>
       </c>
       <c r="F17" s="1">
-        <v>392</v>
+        <v>8</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1852,19 +1843,19 @@
         <v>18</v>
       </c>
       <c r="B18" s="2">
-        <v>2.371657848358154</v>
+        <v>2.105263233184815</v>
       </c>
       <c r="C18" s="1">
-        <v>322</v>
+        <v>274</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
       </c>
       <c r="E18" s="1">
-        <v>314</v>
+        <v>274</v>
       </c>
       <c r="F18" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
@@ -1875,25 +1866,25 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B19" s="2">
-        <v>2.018118858337402</v>
+        <v>1.813292384147644</v>
       </c>
       <c r="C19" s="1">
-        <v>274</v>
+        <v>236</v>
       </c>
       <c r="D19" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E19" s="1">
-        <v>274</v>
+        <v>232</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H19" s="1">
         <v>0</v>
@@ -1901,25 +1892,25 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B20" s="2">
-        <v>1.738233804702759</v>
+        <v>1.38301956653595</v>
       </c>
       <c r="C20" s="1">
-        <v>236</v>
+        <v>180</v>
       </c>
       <c r="D20" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>232</v>
+        <v>180</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H20" s="1">
         <v>0</v>
@@ -1930,16 +1921,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="2">
-        <v>1.325771570205689</v>
+        <v>1.15251636505127</v>
       </c>
       <c r="C21" s="1">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -1956,16 +1947,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="2">
-        <v>1.104809641838074</v>
+        <v>0.7376104593276978</v>
       </c>
       <c r="C22" s="1">
-        <v>150</v>
+        <v>96</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>150</v>
+        <v>96</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -1982,16 +1973,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="2">
-        <v>0.7070781588554382</v>
+        <v>0.3688052296638489</v>
       </c>
       <c r="C23" s="1">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -2008,16 +1999,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="2">
-        <v>0.3535390794277191</v>
+        <v>0.3380714654922485</v>
       </c>
       <c r="C24" s="1">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -2034,16 +2025,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="2">
-        <v>0.3240774869918823</v>
+        <v>0.2766039073467255</v>
       </c>
       <c r="C25" s="1">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
       </c>
       <c r="E25" s="1">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -2060,7 +2051,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2">
-        <v>0.2651543021202087</v>
+        <v>0.2766039073467255</v>
       </c>
       <c r="C26" s="1">
         <v>36</v>
@@ -2086,7 +2077,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="2">
-        <v>0.2651543021202087</v>
+        <v>0.2766039073467255</v>
       </c>
       <c r="C27" s="1">
         <v>36</v>
@@ -2112,16 +2103,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="2">
-        <v>0.2651543021202087</v>
+        <v>0.230503261089325</v>
       </c>
       <c r="C28" s="1">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -2138,7 +2129,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="2">
-        <v>0.2209619134664536</v>
+        <v>0.230503261089325</v>
       </c>
       <c r="C29" s="1">
         <v>30</v>
@@ -2164,16 +2155,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="2">
-        <v>0.2209619134664536</v>
+        <v>0.09220130741596222</v>
       </c>
       <c r="C30" s="1">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -2190,16 +2181,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="2">
-        <v>0.08838476985692978</v>
+        <v>0.06146753579378128</v>
       </c>
       <c r="C31" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -2216,7 +2207,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="2">
-        <v>0.05892317742109299</v>
+        <v>0.06146753579378128</v>
       </c>
       <c r="C32" s="1">
         <v>8</v>
@@ -2239,25 +2230,25 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="B33" s="2">
-        <v>0.05892317742109299</v>
+        <v>0.03073376789689064</v>
       </c>
       <c r="C33" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D33" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E33" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H33" s="1">
         <v>0</v>
@@ -2265,85 +2256,59 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.02946158871054649</v>
+        <v>0.03073376789689064</v>
       </c>
       <c r="C34" s="1">
         <v>4</v>
       </c>
       <c r="D34" s="1">
+        <v>0</v>
+      </c>
+      <c r="E34" s="1">
         <v>4</v>
       </c>
-      <c r="E34" s="1">
-        <v>0</v>
-      </c>
       <c r="F34" s="1">
         <v>0</v>
       </c>
       <c r="G34" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H34" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B35" s="2">
-        <v>0.02946158871054649</v>
-      </c>
-      <c r="C35" s="1">
-        <v>4</v>
-      </c>
-      <c r="D35" s="1">
-        <v>0</v>
-      </c>
-      <c r="E35" s="1">
-        <v>4</v>
-      </c>
-      <c r="F35" s="1">
-        <v>0</v>
-      </c>
-      <c r="G35" s="1">
-        <v>0</v>
-      </c>
-      <c r="H35" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C36">
+      <c r="C35">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D36">
+      <c r="D35">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E36">
+      <c r="E35">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F36">
+      <c r="F35">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G36">
+      <c r="G35">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H36">
+      <c r="H35">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/02_GD32F407_FreeRTOS_Timer/Project/GD32F407_analysis.xlsx
+++ b/02_GD32F407_FreeRTOS_Timer/Project/GD32F407_analysis.xlsx
@@ -285,40 +285,40 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
-                  <c:v>96.21660614013672</c:v>
+                  <c:v>96.2117919921875</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.287430047988892</c:v>
+                  <c:v>1.287365555763245</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.282420516014099</c:v>
+                  <c:v>1.282356381416321</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.001891016960144</c:v>
+                  <c:v>1.001840829849243</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.0801512822508812</c:v>
+                  <c:v>0.08014727383852005</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.07514183223247528</c:v>
+                  <c:v>0.07513806968927383</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.02504727616906166</c:v>
+                  <c:v>0.03005522675812244</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.01127127464860678</c:v>
+                  <c:v>0.01127071026712656</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.005009455140680075</c:v>
+                  <c:v>0.005009204614907503</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.005009455140680075</c:v>
+                  <c:v>0.005009204614907503</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.005009455140680075</c:v>
+                  <c:v>0.005009204614907503</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.005009455140680075</c:v>
+                  <c:v>0.005009204614907503</c:v>
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>0</c:v>
@@ -395,10 +395,10 @@
                   <c:v>tasks.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>queue.o</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>timers.o</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>queue.o</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>port.o</c:v>
@@ -410,16 +410,16 @@
                   <c:v>heap_4.o</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>main.o</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>gd32f4xx_usart.o</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>usart0.o</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>system_gd32f4xx.o</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>main.o</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>printf3.o</c:v>
@@ -500,100 +500,100 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
-                  <c:v>24.21052551269531</c:v>
+                  <c:v>22.12228965759277</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.029196739196777</c:v>
+                  <c:v>13.46998500823975</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.85247802734375</c:v>
+                  <c:v>8.42919921875</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.045716285705566</c:v>
+                  <c:v>7.20211935043335</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.578178882598877</c:v>
+                  <c:v>5.061702728271484</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.101805686950684</c:v>
+                  <c:v>4.629436016082764</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.548597812652588</c:v>
+                  <c:v>4.127449035644531</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.333461284637451</c:v>
+                  <c:v>4.127449035644531</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.102958202362061</c:v>
+                  <c:v>3.932231664657593</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.657318592071533</c:v>
+                  <c:v>3.723070383071899</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.626584768295288</c:v>
+                  <c:v>3.290803909301758</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.611217737197876</c:v>
+                  <c:v>3.276859760284424</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.334613800048828</c:v>
+                  <c:v>3.025866270065308</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.28851318359375</c:v>
+                  <c:v>2.984034061431885</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.212831258773804</c:v>
+                  <c:v>2.007948160171509</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2.105263233184815</c:v>
+                  <c:v>1.910339593887329</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.813292384147644</c:v>
+                  <c:v>1.645401954650879</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.38301956653595</c:v>
+                  <c:v>1.254967570304871</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.15251636505127</c:v>
+                  <c:v>1.045806288719177</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.7376104593276978</c:v>
+                  <c:v>0.6693160533905029</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.3688052296638489</c:v>
+                  <c:v>0.3346580266952515</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.3380714654922485</c:v>
+                  <c:v>0.3067698478698731</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.2766039073467255</c:v>
+                  <c:v>0.2509935200214386</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.2766039073467255</c:v>
+                  <c:v>0.2509935200214386</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.2766039073467255</c:v>
+                  <c:v>0.2509935200214386</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.230503261089325</c:v>
+                  <c:v>0.2091612666845322</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.230503261089325</c:v>
+                  <c:v>0.2091612666845322</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.09220130741596222</c:v>
+                  <c:v>0.08366450667381287</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.06146753579378128</c:v>
+                  <c:v>0.05577633529901505</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.06146753579378128</c:v>
+                  <c:v>0.05577633529901505</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.03073376789689064</c:v>
+                  <c:v>0.02788816764950752</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.03073376789689064</c:v>
+                  <c:v>0.02788816764950752</c:v>
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>0</c:v>
@@ -1060,7 +1060,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>96.21660614013672</v>
+        <v>96.2117919921875</v>
       </c>
       <c r="C3" s="1">
         <v>76828</v>
@@ -1086,7 +1086,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>1.287430047988892</v>
+        <v>1.287365555763245</v>
       </c>
       <c r="C4" s="1">
         <v>1028</v>
@@ -1112,7 +1112,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>1.282420516014099</v>
+        <v>1.282356381416321</v>
       </c>
       <c r="C5" s="1">
         <v>1024</v>
@@ -1138,16 +1138,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>1.001891016960144</v>
+        <v>1.001840829849243</v>
       </c>
       <c r="C6" s="1">
         <v>800</v>
       </c>
       <c r="D6" s="1">
-        <v>3151</v>
+        <v>3173</v>
       </c>
       <c r="E6" s="1">
-        <v>3108</v>
+        <v>3130</v>
       </c>
       <c r="F6" s="1">
         <v>43</v>
@@ -1164,16 +1164,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.0801512822508812</v>
+        <v>0.08014727383852005</v>
       </c>
       <c r="C7" s="1">
         <v>64</v>
       </c>
       <c r="D7" s="1">
-        <v>1022</v>
+        <v>1932</v>
       </c>
       <c r="E7" s="1">
-        <v>1002</v>
+        <v>1912</v>
       </c>
       <c r="F7" s="1">
         <v>20</v>
@@ -1190,16 +1190,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.07514183223247528</v>
+        <v>0.07513806968927383</v>
       </c>
       <c r="C8" s="1">
         <v>60</v>
       </c>
       <c r="D8" s="1">
-        <v>1045</v>
+        <v>1209</v>
       </c>
       <c r="E8" s="1">
-        <v>1024</v>
+        <v>1188</v>
       </c>
       <c r="F8" s="1">
         <v>21</v>
@@ -1216,16 +1216,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.02504727616906166</v>
+        <v>0.03005522675812244</v>
       </c>
       <c r="C9" s="1">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D9" s="1">
-        <v>476</v>
+        <v>592</v>
       </c>
       <c r="E9" s="1">
-        <v>476</v>
+        <v>592</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -1234,7 +1234,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1242,16 +1242,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.01127127464860678</v>
+        <v>0.01127071026712656</v>
       </c>
       <c r="C10" s="1">
         <v>9</v>
       </c>
       <c r="D10" s="1">
-        <v>917</v>
+        <v>1033</v>
       </c>
       <c r="E10" s="1">
-        <v>872</v>
+        <v>988</v>
       </c>
       <c r="F10" s="1">
         <v>41</v>
@@ -1268,7 +1268,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.005009455140680075</v>
+        <v>0.005009204614907503</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
@@ -1294,7 +1294,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.005009455140680075</v>
+        <v>0.005009204614907503</v>
       </c>
       <c r="C12" s="1">
         <v>4</v>
@@ -1320,7 +1320,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.005009455140680075</v>
+        <v>0.005009204614907503</v>
       </c>
       <c r="C13" s="1">
         <v>4</v>
@@ -1346,7 +1346,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.005009455140680075</v>
+        <v>0.005009204614907503</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
@@ -1453,16 +1453,16 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>24.21052551269531</v>
+        <v>22.12228965759277</v>
       </c>
       <c r="C3" s="1">
-        <v>3151</v>
+        <v>3173</v>
       </c>
       <c r="D3" s="1">
         <v>800</v>
       </c>
       <c r="E3" s="1">
-        <v>3108</v>
+        <v>3130</v>
       </c>
       <c r="F3" s="1">
         <v>43</v>
@@ -1476,54 +1476,54 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2">
-        <v>8.029196739196777</v>
+        <v>13.46998500823975</v>
       </c>
       <c r="C4" s="1">
-        <v>1045</v>
+        <v>1932</v>
       </c>
       <c r="D4" s="1">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E4" s="1">
-        <v>1024</v>
+        <v>1912</v>
       </c>
       <c r="F4" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" s="2">
-        <v>7.85247802734375</v>
+        <v>8.42919921875</v>
       </c>
       <c r="C5" s="1">
-        <v>1022</v>
+        <v>1209</v>
       </c>
       <c r="D5" s="1">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E5" s="1">
-        <v>1002</v>
+        <v>1188</v>
       </c>
       <c r="F5" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1531,16 +1531,16 @@
         <v>8</v>
       </c>
       <c r="B6" s="2">
-        <v>7.045716285705566</v>
+        <v>7.20211935043335</v>
       </c>
       <c r="C6" s="1">
-        <v>917</v>
+        <v>1033</v>
       </c>
       <c r="D6" s="1">
         <v>9</v>
       </c>
       <c r="E6" s="1">
-        <v>872</v>
+        <v>988</v>
       </c>
       <c r="F6" s="1">
         <v>41</v>
@@ -1557,7 +1557,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="2">
-        <v>5.578178882598877</v>
+        <v>5.061702728271484</v>
       </c>
       <c r="C7" s="1">
         <v>726</v>
@@ -1583,7 +1583,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="2">
-        <v>5.101805686950684</v>
+        <v>4.629436016082764</v>
       </c>
       <c r="C8" s="1">
         <v>664</v>
@@ -1606,16 +1606,16 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>4.548597812652588</v>
+        <v>4.127449035644531</v>
       </c>
       <c r="C9" s="1">
         <v>592</v>
       </c>
       <c r="D9" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E9" s="1">
         <v>592</v>
@@ -1627,24 +1627,24 @@
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B10" s="2">
-        <v>4.333461284637451</v>
+        <v>4.127449035644531</v>
       </c>
       <c r="C10" s="1">
-        <v>564</v>
+        <v>592</v>
       </c>
       <c r="D10" s="1">
-        <v>1028</v>
+        <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>564</v>
+        <v>592</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -1653,59 +1653,59 @@
         <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>1028</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B11" s="2">
-        <v>4.102958202362061</v>
+        <v>3.932231664657593</v>
       </c>
       <c r="C11" s="1">
-        <v>534</v>
+        <v>564</v>
       </c>
       <c r="D11" s="1">
-        <v>4</v>
+        <v>1028</v>
       </c>
       <c r="E11" s="1">
-        <v>530</v>
+        <v>564</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>3.657318592071533</v>
+        <v>3.723070383071899</v>
       </c>
       <c r="C12" s="1">
-        <v>476</v>
+        <v>534</v>
       </c>
       <c r="D12" s="1">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E12" s="1">
-        <v>476</v>
+        <v>530</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H12" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1713,7 +1713,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="2">
-        <v>3.626584768295288</v>
+        <v>3.290803909301758</v>
       </c>
       <c r="C13" s="1">
         <v>472</v>
@@ -1739,7 +1739,7 @@
         <v>15</v>
       </c>
       <c r="B14" s="2">
-        <v>3.611217737197876</v>
+        <v>3.276859760284424</v>
       </c>
       <c r="C14" s="1">
         <v>470</v>
@@ -1765,7 +1765,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="2">
-        <v>3.334613800048828</v>
+        <v>3.025866270065308</v>
       </c>
       <c r="C15" s="1">
         <v>434</v>
@@ -1791,7 +1791,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="2">
-        <v>3.28851318359375</v>
+        <v>2.984034061431885</v>
       </c>
       <c r="C16" s="1">
         <v>428</v>
@@ -1817,7 +1817,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2">
-        <v>2.212831258773804</v>
+        <v>2.007948160171509</v>
       </c>
       <c r="C17" s="1">
         <v>288</v>
@@ -1843,7 +1843,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="2">
-        <v>2.105263233184815</v>
+        <v>1.910339593887329</v>
       </c>
       <c r="C18" s="1">
         <v>274</v>
@@ -1869,7 +1869,7 @@
         <v>12</v>
       </c>
       <c r="B19" s="2">
-        <v>1.813292384147644</v>
+        <v>1.645401954650879</v>
       </c>
       <c r="C19" s="1">
         <v>236</v>
@@ -1895,7 +1895,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2">
-        <v>1.38301956653595</v>
+        <v>1.254967570304871</v>
       </c>
       <c r="C20" s="1">
         <v>180</v>
@@ -1921,7 +1921,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2">
-        <v>1.15251636505127</v>
+        <v>1.045806288719177</v>
       </c>
       <c r="C21" s="1">
         <v>150</v>
@@ -1947,7 +1947,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2">
-        <v>0.7376104593276978</v>
+        <v>0.6693160533905029</v>
       </c>
       <c r="C22" s="1">
         <v>96</v>
@@ -1973,7 +1973,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2">
-        <v>0.3688052296638489</v>
+        <v>0.3346580266952515</v>
       </c>
       <c r="C23" s="1">
         <v>48</v>
@@ -1999,7 +1999,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2">
-        <v>0.3380714654922485</v>
+        <v>0.3067698478698731</v>
       </c>
       <c r="C24" s="1">
         <v>44</v>
@@ -2025,7 +2025,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="2">
-        <v>0.2766039073467255</v>
+        <v>0.2509935200214386</v>
       </c>
       <c r="C25" s="1">
         <v>36</v>
@@ -2051,7 +2051,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2">
-        <v>0.2766039073467255</v>
+        <v>0.2509935200214386</v>
       </c>
       <c r="C26" s="1">
         <v>36</v>
@@ -2077,7 +2077,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="2">
-        <v>0.2766039073467255</v>
+        <v>0.2509935200214386</v>
       </c>
       <c r="C27" s="1">
         <v>36</v>
@@ -2103,7 +2103,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="2">
-        <v>0.230503261089325</v>
+        <v>0.2091612666845322</v>
       </c>
       <c r="C28" s="1">
         <v>30</v>
@@ -2129,7 +2129,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="2">
-        <v>0.230503261089325</v>
+        <v>0.2091612666845322</v>
       </c>
       <c r="C29" s="1">
         <v>30</v>
@@ -2155,7 +2155,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2">
-        <v>0.09220130741596222</v>
+        <v>0.08366450667381287</v>
       </c>
       <c r="C30" s="1">
         <v>12</v>
@@ -2181,7 +2181,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="2">
-        <v>0.06146753579378128</v>
+        <v>0.05577633529901505</v>
       </c>
       <c r="C31" s="1">
         <v>8</v>
@@ -2207,7 +2207,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="2">
-        <v>0.06146753579378128</v>
+        <v>0.05577633529901505</v>
       </c>
       <c r="C32" s="1">
         <v>8</v>
@@ -2233,7 +2233,7 @@
         <v>10</v>
       </c>
       <c r="B33" s="2">
-        <v>0.03073376789689064</v>
+        <v>0.02788816764950752</v>
       </c>
       <c r="C33" s="1">
         <v>4</v>
@@ -2259,7 +2259,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.03073376789689064</v>
+        <v>0.02788816764950752</v>
       </c>
       <c r="C34" s="1">
         <v>4</v>

--- a/02_GD32F407_FreeRTOS_Timer/Project/GD32F407_analysis.xlsx
+++ b/02_GD32F407_FreeRTOS_Timer/Project/GD32F407_analysis.xlsx
@@ -404,13 +404,13 @@
                   <c:v>port.o</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>main.o</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>mc_w.l</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>heap_4.o</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>main.o</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>gd32f4xx_usart.o</c:v>
@@ -500,100 +500,100 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
-                  <c:v>22.12228965759277</c:v>
+                  <c:v>22.00537872314453</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13.46998500823975</c:v>
+                  <c:v>13.32321929931641</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.42919921875</c:v>
+                  <c:v>8.337355613708496</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.20211935043335</c:v>
+                  <c:v>7.12364673614502</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.061702728271484</c:v>
+                  <c:v>5.047927856445313</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.629436016082764</c:v>
+                  <c:v>5.006551265716553</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.127449035644531</c:v>
+                  <c:v>4.578994750976563</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.127449035644531</c:v>
+                  <c:v>4.08247709274292</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.932231664657593</c:v>
+                  <c:v>3.889386892318726</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.723070383071899</c:v>
+                  <c:v>3.682504653930664</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.290803909301758</c:v>
+                  <c:v>3.254947900772095</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.276859760284424</c:v>
+                  <c:v>3.241155862808228</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.025866270065308</c:v>
+                  <c:v>2.992897033691406</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.984034061431885</c:v>
+                  <c:v>2.951520681381226</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.007948160171509</c:v>
+                  <c:v>1.986069917678833</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.910339593887329</c:v>
+                  <c:v>1.889524817466736</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.645401954650879</c:v>
+                  <c:v>1.627473950386047</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.254967570304871</c:v>
+                  <c:v>1.241293668746948</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.045806288719177</c:v>
+                  <c:v>1.034411430358887</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.6693160533905029</c:v>
+                  <c:v>0.6620233058929443</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.3346580266952515</c:v>
+                  <c:v>0.3310116529464722</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.3067698478698731</c:v>
+                  <c:v>0.3034273386001587</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.2509935200214386</c:v>
+                  <c:v>0.2482587397098541</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.2509935200214386</c:v>
+                  <c:v>0.2482587397098541</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.2509935200214386</c:v>
+                  <c:v>0.2482587397098541</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.2091612666845322</c:v>
+                  <c:v>0.2068822830915451</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.2091612666845322</c:v>
+                  <c:v>0.2068822830915451</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.08366450667381287</c:v>
+                  <c:v>0.08275291323661804</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.05577633529901505</c:v>
+                  <c:v>0.05516861006617546</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.05577633529901505</c:v>
+                  <c:v>0.05516861006617546</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.02788816764950752</c:v>
+                  <c:v>0.02758430503308773</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.02788816764950752</c:v>
+                  <c:v>0.02758430503308773</c:v>
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>0</c:v>
@@ -1144,10 +1144,10 @@
         <v>800</v>
       </c>
       <c r="D6" s="1">
-        <v>3173</v>
+        <v>3191</v>
       </c>
       <c r="E6" s="1">
-        <v>3130</v>
+        <v>3148</v>
       </c>
       <c r="F6" s="1">
         <v>43</v>
@@ -1222,10 +1222,10 @@
         <v>24</v>
       </c>
       <c r="D9" s="1">
-        <v>592</v>
+        <v>732</v>
       </c>
       <c r="E9" s="1">
-        <v>592</v>
+        <v>732</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -1453,16 +1453,16 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>22.12228965759277</v>
+        <v>22.00537872314453</v>
       </c>
       <c r="C3" s="1">
-        <v>3173</v>
+        <v>3191</v>
       </c>
       <c r="D3" s="1">
         <v>800</v>
       </c>
       <c r="E3" s="1">
-        <v>3130</v>
+        <v>3148</v>
       </c>
       <c r="F3" s="1">
         <v>43</v>
@@ -1479,7 +1479,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="2">
-        <v>13.46998500823975</v>
+        <v>13.32321929931641</v>
       </c>
       <c r="C4" s="1">
         <v>1932</v>
@@ -1505,7 +1505,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="2">
-        <v>8.42919921875</v>
+        <v>8.337355613708496</v>
       </c>
       <c r="C5" s="1">
         <v>1209</v>
@@ -1531,7 +1531,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="2">
-        <v>7.20211935043335</v>
+        <v>7.12364673614502</v>
       </c>
       <c r="C6" s="1">
         <v>1033</v>
@@ -1554,80 +1554,80 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" s="2">
-        <v>5.061702728271484</v>
+        <v>5.047927856445313</v>
       </c>
       <c r="C7" s="1">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="D7" s="1">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E7" s="1">
-        <v>722</v>
+        <v>732</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B8" s="2">
-        <v>4.629436016082764</v>
+        <v>5.006551265716553</v>
       </c>
       <c r="C8" s="1">
-        <v>664</v>
+        <v>726</v>
       </c>
       <c r="D8" s="1">
-        <v>76828</v>
+        <v>4</v>
       </c>
       <c r="E8" s="1">
-        <v>626</v>
+        <v>722</v>
       </c>
       <c r="F8" s="1">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H8" s="1">
-        <v>76828</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B9" s="2">
-        <v>4.127449035644531</v>
+        <v>4.578994750976563</v>
       </c>
       <c r="C9" s="1">
-        <v>592</v>
+        <v>664</v>
       </c>
       <c r="D9" s="1">
-        <v>24</v>
+        <v>76828</v>
       </c>
       <c r="E9" s="1">
-        <v>592</v>
+        <v>626</v>
       </c>
       <c r="F9" s="1">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>24</v>
+        <v>76828</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1635,7 +1635,7 @@
         <v>13</v>
       </c>
       <c r="B10" s="2">
-        <v>4.127449035644531</v>
+        <v>4.08247709274292</v>
       </c>
       <c r="C10" s="1">
         <v>592</v>
@@ -1661,7 +1661,7 @@
         <v>2</v>
       </c>
       <c r="B11" s="2">
-        <v>3.932231664657593</v>
+        <v>3.889386892318726</v>
       </c>
       <c r="C11" s="1">
         <v>564</v>
@@ -1687,7 +1687,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>3.723070383071899</v>
+        <v>3.682504653930664</v>
       </c>
       <c r="C12" s="1">
         <v>534</v>
@@ -1713,7 +1713,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="2">
-        <v>3.290803909301758</v>
+        <v>3.254947900772095</v>
       </c>
       <c r="C13" s="1">
         <v>472</v>
@@ -1739,7 +1739,7 @@
         <v>15</v>
       </c>
       <c r="B14" s="2">
-        <v>3.276859760284424</v>
+        <v>3.241155862808228</v>
       </c>
       <c r="C14" s="1">
         <v>470</v>
@@ -1765,7 +1765,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="2">
-        <v>3.025866270065308</v>
+        <v>2.992897033691406</v>
       </c>
       <c r="C15" s="1">
         <v>434</v>
@@ -1791,7 +1791,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="2">
-        <v>2.984034061431885</v>
+        <v>2.951520681381226</v>
       </c>
       <c r="C16" s="1">
         <v>428</v>
@@ -1817,7 +1817,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2">
-        <v>2.007948160171509</v>
+        <v>1.986069917678833</v>
       </c>
       <c r="C17" s="1">
         <v>288</v>
@@ -1843,7 +1843,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="2">
-        <v>1.910339593887329</v>
+        <v>1.889524817466736</v>
       </c>
       <c r="C18" s="1">
         <v>274</v>
@@ -1869,7 +1869,7 @@
         <v>12</v>
       </c>
       <c r="B19" s="2">
-        <v>1.645401954650879</v>
+        <v>1.627473950386047</v>
       </c>
       <c r="C19" s="1">
         <v>236</v>
@@ -1895,7 +1895,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2">
-        <v>1.254967570304871</v>
+        <v>1.241293668746948</v>
       </c>
       <c r="C20" s="1">
         <v>180</v>
@@ -1921,7 +1921,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2">
-        <v>1.045806288719177</v>
+        <v>1.034411430358887</v>
       </c>
       <c r="C21" s="1">
         <v>150</v>
@@ -1947,7 +1947,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2">
-        <v>0.6693160533905029</v>
+        <v>0.6620233058929443</v>
       </c>
       <c r="C22" s="1">
         <v>96</v>
@@ -1973,7 +1973,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2">
-        <v>0.3346580266952515</v>
+        <v>0.3310116529464722</v>
       </c>
       <c r="C23" s="1">
         <v>48</v>
@@ -1999,7 +1999,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2">
-        <v>0.3067698478698731</v>
+        <v>0.3034273386001587</v>
       </c>
       <c r="C24" s="1">
         <v>44</v>
@@ -2025,7 +2025,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="2">
-        <v>0.2509935200214386</v>
+        <v>0.2482587397098541</v>
       </c>
       <c r="C25" s="1">
         <v>36</v>
@@ -2051,7 +2051,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2">
-        <v>0.2509935200214386</v>
+        <v>0.2482587397098541</v>
       </c>
       <c r="C26" s="1">
         <v>36</v>
@@ -2077,7 +2077,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="2">
-        <v>0.2509935200214386</v>
+        <v>0.2482587397098541</v>
       </c>
       <c r="C27" s="1">
         <v>36</v>
@@ -2103,7 +2103,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="2">
-        <v>0.2091612666845322</v>
+        <v>0.2068822830915451</v>
       </c>
       <c r="C28" s="1">
         <v>30</v>
@@ -2129,7 +2129,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="2">
-        <v>0.2091612666845322</v>
+        <v>0.2068822830915451</v>
       </c>
       <c r="C29" s="1">
         <v>30</v>
@@ -2155,7 +2155,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2">
-        <v>0.08366450667381287</v>
+        <v>0.08275291323661804</v>
       </c>
       <c r="C30" s="1">
         <v>12</v>
@@ -2181,7 +2181,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="2">
-        <v>0.05577633529901505</v>
+        <v>0.05516861006617546</v>
       </c>
       <c r="C31" s="1">
         <v>8</v>
@@ -2207,7 +2207,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="2">
-        <v>0.05577633529901505</v>
+        <v>0.05516861006617546</v>
       </c>
       <c r="C32" s="1">
         <v>8</v>
@@ -2233,7 +2233,7 @@
         <v>10</v>
       </c>
       <c r="B33" s="2">
-        <v>0.02788816764950752</v>
+        <v>0.02758430503308773</v>
       </c>
       <c r="C33" s="1">
         <v>4</v>
@@ -2259,7 +2259,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.02788816764950752</v>
+        <v>0.02758430503308773</v>
       </c>
       <c r="C34" s="1">
         <v>4</v>
